--- a/sheets/조재수대금교본/검수/장윤정 목포행 완행열차.xlsx
+++ b/sheets/조재수대금교본/검수/장윤정 목포행 완행열차.xlsx
@@ -3983,7 +3983,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅅ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -4062,8 +4062,7 @@
         <is>
           <t xml:space="preserve">–
 –
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -4092,11 +4091,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="23"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
@@ -4120,17 +4115,9 @@
         </is>
       </c>
       <c r="K5" s="23"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="23"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="23"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
@@ -4163,11 +4150,7 @@
       <c r="E6" s="24"/>
       <c r="F6" s="21"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -4214,7 +4197,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㅅ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -4224,9 +4207,8 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽
-–
-Z</t>
+          <t xml:space="preserve">㴌
+–</t>
         </is>
       </c>
       <c r="I7" s="22"/>
@@ -4306,8 +4288,7 @@
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I9" s="23"/>
@@ -4330,11 +4311,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4503,26 +4480,25 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㅂ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-潢
-–
-‹</t>
-        </is>
-      </c>
-      <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 潢
 –</t>
         </is>
       </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢
+–</t>
+        </is>
+      </c>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4544,8 +4520,7 @@
         <is>
           <t xml:space="preserve">潢
 南
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
@@ -4568,12 +4543,7 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
@@ -4628,7 +4598,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅅ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C15" s="22"/>
@@ -4636,7 +4606,7 @@
       <c r="E15" s="22"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅂ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G15" s="22"/>
@@ -4654,7 +4624,7 @@
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M15" s="22"/>

--- a/sheets/조재수대금교본/검수/장윤정 목포행 완행열차.xlsx
+++ b/sheets/조재수대금교본/검수/장윤정 목포행 완행열차.xlsx
@@ -3983,7 +3983,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅅ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -4197,7 +4197,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㅅ</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -4207,8 +4207,9 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-–</t>
+          <t xml:space="preserve">㴌∽
+–
+Z</t>
         </is>
       </c>
       <c r="I7" s="22"/>
@@ -4480,7 +4481,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㅂ</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -4543,7 +4544,11 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
@@ -4598,7 +4603,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅅ</t>
         </is>
       </c>
       <c r="C15" s="22"/>
@@ -4606,7 +4611,7 @@
       <c r="E15" s="22"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅂ</t>
         </is>
       </c>
       <c r="G15" s="22"/>
@@ -4624,7 +4629,7 @@
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="M15" s="22"/>

--- a/sheets/조재수대금교본/검수/장윤정 목포행 완행열차.xlsx
+++ b/sheets/조재수대금교본/검수/장윤정 목포행 완행열차.xlsx
@@ -3931,30 +3931,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="105.26" customHeight="true">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="117.77" customHeight="true">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="117.77" customHeight="true">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="117.77" customHeight="true">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="117.77" customHeight="true">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="117.77" customHeight="true">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="117.77" customHeight="true">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -4275,7 +4275,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" ht="117.77" customHeight="true">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -4308,7 +4308,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="117.77" customHeight="true">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" ht="117.77" customHeight="true">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="117.77" customHeight="true">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="S12" s="23"/>
     </row>
-    <row r="13" ht="117.77" customHeight="true">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="117.77" customHeight="true">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="117.77" customHeight="true">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="117.77" customHeight="true">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4679,7 +4679,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" ht="117.77" customHeight="true">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4704,7 +4704,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" ht="117.77" customHeight="true">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4777,6 +4777,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="38"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
 </worksheet>
 </file>